--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -1838,7 +1838,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='marston']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='marston']</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='marston']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='marston']</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='hewlett_randolph']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='hewlett_randolph']</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='hewlett_randolph']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='hewlett_randolph']</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='hewlett_randolph']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='hewlett_randolph']</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='hewlett_randolph']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='hewlett_randolph']</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='zaeske']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='zaeske']</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='adapted_terzaghi']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='adapted_terzaghi']</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='prandtl']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='prandtl']</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='fhwa_parabolic']</t>
+          <t>ancestor::diggs:ArchingCoefficient/diggs:archingModel[.='fhwa_parabolic']</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as fixed schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices or vary too freely to justify a fixed schema element - the geometry and stiffness ratios that gate whether an arching method's unit-cell idealisation applies to a given layout, open-ended since a future method may add its own - carried in diggs:RITreatedAreaDesignType/methodApplicabilityRatio. The active earth pressure coefficient, once considered for this dictionary, turned out not to need it: a single, always-the-same-formula quantity, now the typed element diggs:RILTPDesignType/activeEarthPressureCoefficient instead. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:RILTPDesignType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
+          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as fixed schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices or vary too freely to justify a fixed schema element - the geometry and stiffness ratios that gate whether an arching method's unit-cell idealisation applies to a given layout, open-ended since a future method may add its own - carried in diggs:DesignRITreatedAreaType/methodApplicabilityRatio. The active earth pressure coefficient, once considered for this dictionary, turned out not to need it: a single, always-the-same-formula quantity, now the typed element diggs:DesignRILTPType/activeEarthPressureCoefficient instead. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:DesignRILTPType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
         </is>
       </c>
     </row>
